--- a/InputData/fuels/ETRbF/Export Tax Rate by Fuel.xlsx
+++ b/InputData/fuels/ETRbF/Export Tax Rate by Fuel.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deept\OneDrive\Desktop\Input Data for India 2.0\fuels\ETRbF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\fuels\ETRbF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676C6D01-7432-44D8-A365-256BD40940CF}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25815" windowHeight="9795"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,17 +25,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>Patrick Watson</t>
+  </si>
+  <si>
+    <t>The U.S. Has Never Had a Tax on Exports</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
     <t>According to Encyclopedia Britannica:</t>
   </si>
   <si>
+    <t>https://www.forbes.com/sites/patrickwwatson/2017/02/13/the-us-has-never-had-a-tax-on-exports/</t>
+  </si>
+  <si>
     <t>Export duties are no longer used to a great extent, except to tax certain mineral, petroleum, and agricultural</t>
   </si>
   <si>
@@ -116,39 +124,12 @@
   </si>
   <si>
     <t>Export Tax Rate (dimensionless)</t>
-  </si>
-  <si>
-    <t>Central Board of Indirect Taxes and Customs</t>
-  </si>
-  <si>
-    <t>Zero Rating of Supplies in GST</t>
-  </si>
-  <si>
-    <t>http://www.cbic.gov.in/resources//htdocs-cbec/gst/51_GST_Flyer_Chapter24.pdf;jsessionid=C74A154D0501A7E845CD0069D425440D</t>
-  </si>
-  <si>
-    <t>Section on "What is Zero Rating", Page 201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In India, with the implementation of Goods and Services Tax (GST) in 2017, exports of goods and services are </t>
-  </si>
-  <si>
-    <t>exempt from taxes. This is as per Section 16(1) of the IGST Act, 2017 which states that "zero rated supply" means</t>
-  </si>
-  <si>
-    <t>any of the following supplies of goods or services or both, namely:</t>
-  </si>
-  <si>
-    <t>a) export of goods or services or both;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b) supply  of  goods  or  services  or  both  to  a  Special  Economic  Zone developer or a Special Economic Zone unit. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -493,105 +474,75 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="91.42578125" customWidth="1"/>
+    <col min="2" max="2" width="91.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="3">
         <v>2017</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A11" r:id="rId1" location="ref592273" display="https://www.britannica.com/topic/tariff - ref592273" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B6" r:id="rId2" xr:uid="{E42BED96-0B23-40BA-A35A-B1466AC7B296}"/>
+    <hyperlink ref="B6" r:id="rId1"/>
+    <hyperlink ref="A11" r:id="rId2" location="ref592273" display="https://www.britannica.com/topic/tariff - ref592273"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -599,186 +550,186 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.59765625" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
       <c r="B20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B22">
         <v>0</v>

--- a/InputData/fuels/ETRbF/Export Tax Rate by Fuel.xlsx
+++ b/InputData/fuels/ETRbF/Export Tax Rate by Fuel.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\fuels\ETRbF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deept\OneDrive\Desktop\Input Data for India 2.0\fuels\ETRbF\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676C6D01-7432-44D8-A365-256BD40940CF}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25815" windowHeight="9795"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -25,26 +26,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Source:</t>
   </si>
   <si>
-    <t>Patrick Watson</t>
-  </si>
-  <si>
-    <t>The U.S. Has Never Had a Tax on Exports</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
     <t>According to Encyclopedia Britannica:</t>
   </si>
   <si>
-    <t>https://www.forbes.com/sites/patrickwwatson/2017/02/13/the-us-has-never-had-a-tax-on-exports/</t>
-  </si>
-  <si>
     <t>Export duties are no longer used to a great extent, except to tax certain mineral, petroleum, and agricultural</t>
   </si>
   <si>
@@ -125,11 +117,38 @@
   <si>
     <t>Export Tax Rate (dimensionless)</t>
   </si>
+  <si>
+    <t>Central Board of Indirect Taxes and Customs</t>
+  </si>
+  <si>
+    <t>Zero Rating of Supplies in GST</t>
+  </si>
+  <si>
+    <t>http://www.cbic.gov.in/resources//htdocs-cbec/gst/51_GST_Flyer_Chapter24.pdf;jsessionid=C74A154D0501A7E845CD0069D425440D</t>
+  </si>
+  <si>
+    <t>Section on "What is Zero Rating", Page 201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In India, with the implementation of Goods and Services Tax (GST) in 2017, exports of goods and services are </t>
+  </si>
+  <si>
+    <t>exempt from taxes. This is as per Section 16(1) of the IGST Act, 2017 which states that "zero rated supply" means</t>
+  </si>
+  <si>
+    <t>any of the following supplies of goods or services or both, namely:</t>
+  </si>
+  <si>
+    <t>a) export of goods or services or both;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b) supply  of  goods  or  services  or  both  to  a  Special  Economic  Zone developer or a Special Economic Zone unit. </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -474,75 +493,105 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="91.3984375" customWidth="1"/>
+    <col min="2" max="2" width="91.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>2017</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B6" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>8</v>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
-    <hyperlink ref="A11" r:id="rId2" location="ref592273" display="https://www.britannica.com/topic/tariff - ref592273"/>
+    <hyperlink ref="A11" r:id="rId1" location="ref592273" display="https://www.britannica.com/topic/tariff - ref592273" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B6" r:id="rId2" xr:uid="{E42BED96-0B23-40BA-A35A-B1466AC7B296}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -550,186 +599,186 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.59765625" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" s="5" t="s">
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>27</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>28</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>31</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -738,4 +787,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BBBBD4E-D992-499B-BCC0-5BFDE3E033C0}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{142CC448-BDCC-451A-9EB2-B2D48CD8FC71}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87253F36-85A0-400B-8260-EAF7A75AD2F2}"/>
 </file>